--- a/Data_processed/env_monthly.xlsx
+++ b/Data_processed/env_monthly.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\GDrive\Academicos\Articulos\Pendientes\Varadero growth rates\Data_processed\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18A297AA-EE88-4701-8CBF-D75894056927}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B721A54A-EB9C-4B51-988C-58F6333D0920}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -25750,7 +25750,7 @@
         <v>1956.9999999855499</v>
       </c>
       <c r="D709" s="10">
-        <v>235.61809999999997</v>
+        <v>235.61809999999994</v>
       </c>
       <c r="E709" s="6">
         <v>8188.9999999999991</v>
@@ -25779,7 +25779,7 @@
         <v>1956.9166666521901</v>
       </c>
       <c r="D710" s="10">
-        <v>-33.799999999999997</v>
+        <v>253.0331666666666</v>
       </c>
       <c r="E710" s="9">
         <v>8718.3333333333321</v>
@@ -25808,7 +25808,7 @@
         <v>1956.83333331883</v>
       </c>
       <c r="D711" s="10">
-        <v>-33.799999999999997</v>
+        <v>270.44823333333329</v>
       </c>
       <c r="E711" s="9">
         <v>9247.6666666666661</v>
@@ -26127,7 +26127,7 @@
         <v>1955.9166666518699</v>
       </c>
       <c r="D722" s="10">
-        <v>-33.799999999999997</v>
+        <v>317.02366666666666</v>
       </c>
       <c r="E722" s="9">
         <v>10663.333333333332</v>
@@ -26156,7 +26156,7 @@
         <v>1955.8333333185101</v>
       </c>
       <c r="D723" s="10">
-        <v>-33.799999999999997</v>
+        <v>316.34373333333332</v>
       </c>
       <c r="E723" s="9">
         <v>10642.666666666666</v>
